--- a/MEZİTLİ.xlsx
+++ b/MEZİTLİ.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J164"/>
+  <dimension ref="A1:K164"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -431,6 +431,9 @@
       <c r="J1" t="str">
         <v>Tescil Önceliği</v>
       </c>
+      <c r="K1" t="str">
+        <v>İşlem Tarihi</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -711,7 +714,7 @@
         <v>Yol</v>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>Onaylandı(Firmaya İletildi)</v>
       </c>
       <c r="I10" t="str">
         <v/>
@@ -719,6 +722,9 @@
       <c r="J10" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K10" t="str">
+        <v>2026-04-08</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -5650,7 +5656,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J164"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K164"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/MEZİTLİ.xlsx
+++ b/MEZİTLİ.xlsx
@@ -1517,13 +1517,16 @@
         <v>Park</v>
       </c>
       <c r="H35" t="str">
-        <v/>
+        <v>Onaylandı(Firmaya İletildi)</v>
       </c>
       <c r="I35" t="str">
         <v/>
       </c>
       <c r="J35" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
+      </c>
+      <c r="K35" t="str">
+        <v>2026-04-08</v>
       </c>
     </row>
     <row r="36">

--- a/MEZİTLİ.xlsx
+++ b/MEZİTLİ.xlsx
@@ -1197,13 +1197,16 @@
         <v>Park</v>
       </c>
       <c r="H25" t="str">
-        <v/>
+        <v>Onaylandı(Firmaya İletildi)</v>
       </c>
       <c r="I25" t="str">
         <v/>
       </c>
       <c r="J25" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
+      </c>
+      <c r="K25" t="str">
+        <v>2026-04-08</v>
       </c>
     </row>
     <row r="26">

--- a/MEZİTLİ.xlsx
+++ b/MEZİTLİ.xlsx
@@ -1232,13 +1232,16 @@
         <v>Park</v>
       </c>
       <c r="H26" t="str">
-        <v/>
+        <v>Onaylandı(Firmaya İletildi)</v>
       </c>
       <c r="I26" t="str">
         <v/>
       </c>
       <c r="J26" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
+      </c>
+      <c r="K26" t="str">
+        <v>2026-04-08</v>
       </c>
     </row>
     <row r="27">

--- a/MEZİTLİ.xlsx
+++ b/MEZİTLİ.xlsx
@@ -1363,13 +1363,16 @@
         <v>Park</v>
       </c>
       <c r="H30" t="str">
-        <v/>
+        <v>Onaylandı(Firmaya İletildi)</v>
       </c>
       <c r="I30" t="str">
         <v/>
       </c>
       <c r="J30" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
+      </c>
+      <c r="K30" t="str">
+        <v>2026-04-08</v>
       </c>
     </row>
     <row r="31">

--- a/MEZİTLİ.xlsx
+++ b/MEZİTLİ.xlsx
@@ -1430,13 +1430,16 @@
         <v>Park</v>
       </c>
       <c r="H32" t="str">
-        <v/>
+        <v>Onaylandı(Firmaya İletildi)</v>
       </c>
       <c r="I32" t="str">
         <v/>
       </c>
       <c r="J32" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
+      </c>
+      <c r="K32" t="str">
+        <v>2026-04-08</v>
       </c>
     </row>
     <row r="33">

--- a/MEZİTLİ.xlsx
+++ b/MEZİTLİ.xlsx
@@ -1497,13 +1497,16 @@
         <v>Park</v>
       </c>
       <c r="H34" t="str">
-        <v/>
+        <v>Onaylandı(Firmaya İletildi)</v>
       </c>
       <c r="I34" t="str">
         <v/>
       </c>
       <c r="J34" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
+      </c>
+      <c r="K34" t="str">
+        <v>2026-04-08</v>
       </c>
     </row>
     <row r="35">

--- a/MEZİTLİ.xlsx
+++ b/MEZİTLİ.xlsx
@@ -1663,13 +1663,16 @@
         <v>Park</v>
       </c>
       <c r="H39" t="str">
-        <v/>
+        <v>Onaylandı(Firmaya İletildi)</v>
       </c>
       <c r="I39" t="str">
         <v/>
       </c>
       <c r="J39" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
+      </c>
+      <c r="K39" t="str">
+        <v>2026-04-08</v>
       </c>
     </row>
     <row r="40">

--- a/MEZİTLİ.xlsx
+++ b/MEZİTLİ.xlsx
@@ -1698,13 +1698,16 @@
         <v>Park</v>
       </c>
       <c r="H40" t="str">
-        <v/>
+        <v>Onaylandı(Firmaya İletildi)</v>
       </c>
       <c r="I40" t="str">
         <v/>
       </c>
       <c r="J40" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
+      </c>
+      <c r="K40" t="str">
+        <v>2026-04-08</v>
       </c>
     </row>
     <row r="41">

--- a/MEZİTLİ.xlsx
+++ b/MEZİTLİ.xlsx
@@ -1733,13 +1733,16 @@
         <v>Park</v>
       </c>
       <c r="H41" t="str">
-        <v/>
+        <v>Onaylandı(Firmaya İletildi)</v>
       </c>
       <c r="I41" t="str">
         <v/>
       </c>
       <c r="J41" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
+      </c>
+      <c r="K41" t="str">
+        <v>2026-04-08</v>
       </c>
     </row>
     <row r="42">

--- a/MEZİTLİ.xlsx
+++ b/MEZİTLİ.xlsx
@@ -1832,13 +1832,16 @@
         <v>Park</v>
       </c>
       <c r="H44" t="str">
-        <v/>
+        <v>Onaylandı(Firmaya İletildi)</v>
       </c>
       <c r="I44" t="str">
         <v/>
       </c>
       <c r="J44" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
+      </c>
+      <c r="K44" t="str">
+        <v>2026-04-08</v>
       </c>
     </row>
     <row r="45">

--- a/MEZİTLİ.xlsx
+++ b/MEZİTLİ.xlsx
@@ -1005,13 +1005,16 @@
         <v>Park</v>
       </c>
       <c r="H19" t="str">
-        <v/>
+        <v>Onaylandı(Firmaya İletildi)</v>
       </c>
       <c r="I19" t="str">
         <v/>
       </c>
       <c r="J19" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
+      </c>
+      <c r="K19" t="str">
+        <v>2026-04-08</v>
       </c>
     </row>
     <row r="20">

--- a/MEZİTLİ.xlsx
+++ b/MEZİTLİ.xlsx
@@ -1104,13 +1104,16 @@
         <v>Park</v>
       </c>
       <c r="H22" t="str">
-        <v/>
+        <v>Onaylandı(Firmaya İletildi)</v>
       </c>
       <c r="I22" t="str">
         <v/>
       </c>
       <c r="J22" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
+      </c>
+      <c r="K22" t="str">
+        <v>2026-04-08</v>
       </c>
     </row>
     <row r="23">

--- a/MEZİTLİ.xlsx
+++ b/MEZİTLİ.xlsx
@@ -1139,13 +1139,16 @@
         <v>Park</v>
       </c>
       <c r="H23" t="str">
-        <v/>
+        <v>Onaylandı(Firmaya İletildi)</v>
       </c>
       <c r="I23" t="str">
         <v/>
       </c>
       <c r="J23" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
+      </c>
+      <c r="K23" t="str">
+        <v>2026-04-08</v>
       </c>
     </row>
     <row r="24">

--- a/MEZİTLİ.xlsx
+++ b/MEZİTLİ.xlsx
@@ -466,6 +466,9 @@
       <c r="J2" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -498,6 +501,9 @@
       <c r="J3" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -530,6 +536,9 @@
       <c r="J4" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -554,7 +563,7 @@
         <v>Yol</v>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>Onaylandı(Firmaya İletildi)</v>
       </c>
       <c r="I5" t="str">
         <v/>
@@ -562,6 +571,9 @@
       <c r="J5" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K5" t="str">
+        <v>2026-04-08</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -594,6 +606,9 @@
       <c r="J6" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -626,6 +641,9 @@
       <c r="J7" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -658,6 +676,9 @@
       <c r="J8" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -690,6 +711,9 @@
       <c r="J9" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -757,6 +781,9 @@
       <c r="J11" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -789,6 +816,9 @@
       <c r="J12" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -821,6 +851,9 @@
       <c r="J13" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -853,6 +886,9 @@
       <c r="J14" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -885,6 +921,9 @@
       <c r="J15" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -917,6 +956,9 @@
       <c r="J16" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -949,6 +991,9 @@
       <c r="J17" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -981,6 +1026,9 @@
       <c r="J18" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -1048,6 +1096,9 @@
       <c r="J20" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -1080,6 +1131,9 @@
       <c r="J21" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -1182,6 +1236,9 @@
       <c r="J24" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
@@ -1284,6 +1341,9 @@
       <c r="J27" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K27" t="str">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
@@ -1316,6 +1376,9 @@
       <c r="J28" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K28" t="str">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
@@ -1348,6 +1411,9 @@
       <c r="J29" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K29" t="str">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -1415,6 +1481,9 @@
       <c r="J31" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K31" t="str">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
@@ -1482,6 +1551,9 @@
       <c r="J33" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K33" t="str">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
@@ -1584,6 +1656,9 @@
       <c r="J36" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K36" t="str">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
@@ -1616,6 +1691,9 @@
       <c r="J37" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K37" t="str">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
@@ -1648,6 +1726,9 @@
       <c r="J38" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K38" t="str">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
@@ -1785,6 +1866,9 @@
       <c r="J42" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K42" t="str">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
@@ -1817,6 +1901,9 @@
       <c r="J43" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K43" t="str">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
@@ -1884,6 +1971,9 @@
       <c r="J45" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K45" t="str">
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
@@ -1916,6 +2006,9 @@
       <c r="J46" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K46" t="str">
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
@@ -1948,6 +2041,9 @@
       <c r="J47" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K47" t="str">
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
@@ -1980,6 +2076,9 @@
       <c r="J48" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K48" t="str">
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
@@ -2012,6 +2111,9 @@
       <c r="J49" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K49" t="str">
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -2044,6 +2146,9 @@
       <c r="J50" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K50" t="str">
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
@@ -2076,6 +2181,9 @@
       <c r="J51" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K51" t="str">
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
@@ -2108,6 +2216,9 @@
       <c r="J52" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K52" t="str">
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
@@ -2140,6 +2251,9 @@
       <c r="J53" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K53" t="str">
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
@@ -2172,6 +2286,9 @@
       <c r="J54" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K54" t="str">
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
@@ -2204,6 +2321,9 @@
       <c r="J55" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K55" t="str">
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
@@ -2236,6 +2356,9 @@
       <c r="J56" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K56" t="str">
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
@@ -2268,6 +2391,9 @@
       <c r="J57" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K57" t="str">
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
@@ -2300,6 +2426,9 @@
       <c r="J58" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K58" t="str">
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
@@ -2332,6 +2461,9 @@
       <c r="J59" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K59" t="str">
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
@@ -2364,6 +2496,9 @@
       <c r="J60" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K60" t="str">
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
@@ -2396,6 +2531,9 @@
       <c r="J61" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K61" t="str">
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
@@ -2428,6 +2566,9 @@
       <c r="J62" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K62" t="str">
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
@@ -2460,6 +2601,9 @@
       <c r="J63" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K63" t="str">
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
@@ -2492,6 +2636,9 @@
       <c r="J64" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K64" t="str">
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
@@ -2524,6 +2671,9 @@
       <c r="J65" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K65" t="str">
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
@@ -2556,6 +2706,9 @@
       <c r="J66" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K66" t="str">
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
@@ -2588,6 +2741,9 @@
       <c r="J67" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K67" t="str">
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
@@ -2620,6 +2776,9 @@
       <c r="J68" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K68" t="str">
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
@@ -2652,6 +2811,9 @@
       <c r="J69" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K69" t="str">
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
@@ -2684,6 +2846,9 @@
       <c r="J70" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K70" t="str">
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
@@ -2716,6 +2881,9 @@
       <c r="J71" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K71" t="str">
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
@@ -2748,6 +2916,9 @@
       <c r="J72" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K72" t="str">
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
@@ -2780,6 +2951,9 @@
       <c r="J73" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K73" t="str">
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
@@ -2812,6 +2986,9 @@
       <c r="J74" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K74" t="str">
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
@@ -2844,6 +3021,9 @@
       <c r="J75" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K75" t="str">
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
@@ -2876,6 +3056,9 @@
       <c r="J76" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K76" t="str">
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
@@ -2908,6 +3091,9 @@
       <c r="J77" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K77" t="str">
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
@@ -2940,6 +3126,9 @@
       <c r="J78" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K78" t="str">
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
@@ -2972,6 +3161,9 @@
       <c r="J79" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K79" t="str">
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
@@ -3004,6 +3196,9 @@
       <c r="J80" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K80" t="str">
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
@@ -3036,6 +3231,9 @@
       <c r="J81" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K81" t="str">
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
@@ -3068,6 +3266,9 @@
       <c r="J82" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K82" t="str">
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
@@ -3100,6 +3301,9 @@
       <c r="J83" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K83" t="str">
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
@@ -3132,6 +3336,9 @@
       <c r="J84" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K84" t="str">
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
@@ -3164,6 +3371,9 @@
       <c r="J85" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K85" t="str">
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
@@ -3196,6 +3406,9 @@
       <c r="J86" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K86" t="str">
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
@@ -3228,6 +3441,9 @@
       <c r="J87" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K87" t="str">
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
@@ -3260,6 +3476,9 @@
       <c r="J88" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K88" t="str">
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
@@ -3292,6 +3511,9 @@
       <c r="J89" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K89" t="str">
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
@@ -3324,6 +3546,9 @@
       <c r="J90" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K90" t="str">
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
@@ -3356,6 +3581,9 @@
       <c r="J91" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K91" t="str">
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
@@ -3388,6 +3616,9 @@
       <c r="J92" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K92" t="str">
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
@@ -3420,6 +3651,9 @@
       <c r="J93" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K93" t="str">
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
@@ -3452,6 +3686,9 @@
       <c r="J94" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K94" t="str">
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
@@ -3484,6 +3721,9 @@
       <c r="J95" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K95" t="str">
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
@@ -3516,6 +3756,9 @@
       <c r="J96" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K96" t="str">
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
@@ -3548,6 +3791,9 @@
       <c r="J97" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K97" t="str">
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
@@ -3580,6 +3826,9 @@
       <c r="J98" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K98" t="str">
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
@@ -3612,6 +3861,9 @@
       <c r="J99" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K99" t="str">
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
@@ -3644,6 +3896,9 @@
       <c r="J100" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K100" t="str">
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
@@ -3676,6 +3931,9 @@
       <c r="J101" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K101" t="str">
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
@@ -3708,6 +3966,9 @@
       <c r="J102" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K102" t="str">
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
@@ -3740,6 +4001,9 @@
       <c r="J103" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K103" t="str">
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
@@ -3772,6 +4036,9 @@
       <c r="J104" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K104" t="str">
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
@@ -3804,6 +4071,9 @@
       <c r="J105" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K105" t="str">
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
@@ -3836,6 +4106,9 @@
       <c r="J106" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K106" t="str">
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
@@ -3868,6 +4141,9 @@
       <c r="J107" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K107" t="str">
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
@@ -3900,6 +4176,9 @@
       <c r="J108" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K108" t="str">
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
@@ -3932,6 +4211,9 @@
       <c r="J109" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K109" t="str">
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
@@ -3964,6 +4246,9 @@
       <c r="J110" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K110" t="str">
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
@@ -3996,6 +4281,9 @@
       <c r="J111" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K111" t="str">
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
@@ -4028,6 +4316,9 @@
       <c r="J112" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K112" t="str">
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
@@ -4060,6 +4351,9 @@
       <c r="J113" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K113" t="str">
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
@@ -4092,6 +4386,9 @@
       <c r="J114" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K114" t="str">
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
@@ -4124,6 +4421,9 @@
       <c r="J115" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K115" t="str">
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
@@ -4156,6 +4456,9 @@
       <c r="J116" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K116" t="str">
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
@@ -4188,6 +4491,9 @@
       <c r="J117" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K117" t="str">
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
@@ -4220,6 +4526,9 @@
       <c r="J118" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K118" t="str">
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
@@ -4252,6 +4561,9 @@
       <c r="J119" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K119" t="str">
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
@@ -4284,6 +4596,9 @@
       <c r="J120" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K120" t="str">
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
@@ -4316,6 +4631,9 @@
       <c r="J121" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K121" t="str">
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
@@ -4348,6 +4666,9 @@
       <c r="J122" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K122" t="str">
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
@@ -4380,6 +4701,9 @@
       <c r="J123" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K123" t="str">
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
@@ -4412,6 +4736,9 @@
       <c r="J124" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K124" t="str">
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
@@ -4444,6 +4771,9 @@
       <c r="J125" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K125" t="str">
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
@@ -4476,6 +4806,9 @@
       <c r="J126" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K126" t="str">
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
@@ -4508,6 +4841,9 @@
       <c r="J127" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K127" t="str">
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
@@ -4540,6 +4876,9 @@
       <c r="J128" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K128" t="str">
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
@@ -4572,6 +4911,9 @@
       <c r="J129" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K129" t="str">
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
@@ -4604,6 +4946,9 @@
       <c r="J130" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K130" t="str">
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
@@ -4636,6 +4981,9 @@
       <c r="J131" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K131" t="str">
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
@@ -4668,6 +5016,9 @@
       <c r="J132" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K132" t="str">
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
@@ -4700,6 +5051,9 @@
       <c r="J133" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K133" t="str">
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
@@ -4732,6 +5086,9 @@
       <c r="J134" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K134" t="str">
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
@@ -4764,6 +5121,9 @@
       <c r="J135" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K135" t="str">
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
@@ -4796,6 +5156,9 @@
       <c r="J136" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K136" t="str">
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
@@ -4828,6 +5191,9 @@
       <c r="J137" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K137" t="str">
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
@@ -4860,6 +5226,9 @@
       <c r="J138" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K138" t="str">
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
@@ -4892,6 +5261,9 @@
       <c r="J139" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K139" t="str">
+        <v/>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
@@ -4924,6 +5296,9 @@
       <c r="J140" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K140" t="str">
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
@@ -4956,6 +5331,9 @@
       <c r="J141" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K141" t="str">
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
@@ -4988,6 +5366,9 @@
       <c r="J142" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K142" t="str">
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
@@ -5020,6 +5401,9 @@
       <c r="J143" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K143" t="str">
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
@@ -5052,6 +5436,9 @@
       <c r="J144" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K144" t="str">
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
@@ -5084,6 +5471,9 @@
       <c r="J145" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K145" t="str">
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
@@ -5116,6 +5506,9 @@
       <c r="J146" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K146" t="str">
+        <v/>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
@@ -5148,6 +5541,9 @@
       <c r="J147" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K147" t="str">
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
@@ -5180,6 +5576,9 @@
       <c r="J148" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K148" t="str">
+        <v/>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
@@ -5212,6 +5611,9 @@
       <c r="J149" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K149" t="str">
+        <v/>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
@@ -5244,6 +5646,9 @@
       <c r="J150" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K150" t="str">
+        <v/>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
@@ -5276,6 +5681,9 @@
       <c r="J151" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K151" t="str">
+        <v/>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
@@ -5308,6 +5716,9 @@
       <c r="J152" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K152" t="str">
+        <v/>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
@@ -5340,6 +5751,9 @@
       <c r="J153" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K153" t="str">
+        <v/>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
@@ -5372,6 +5786,9 @@
       <c r="J154" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K154" t="str">
+        <v/>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
@@ -5404,6 +5821,9 @@
       <c r="J155" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K155" t="str">
+        <v/>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
@@ -5436,6 +5856,9 @@
       <c r="J156" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K156" t="str">
+        <v/>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
@@ -5468,6 +5891,9 @@
       <c r="J157" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K157" t="str">
+        <v/>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
@@ -5500,6 +5926,9 @@
       <c r="J158" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K158" t="str">
+        <v/>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
@@ -5532,6 +5961,9 @@
       <c r="J159" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K159" t="str">
+        <v/>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
@@ -5564,6 +5996,9 @@
       <c r="J160" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K160" t="str">
+        <v/>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
@@ -5596,6 +6031,9 @@
       <c r="J161" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K161" t="str">
+        <v/>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
@@ -5628,6 +6066,9 @@
       <c r="J162" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K162" t="str">
+        <v/>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
@@ -5660,6 +6101,9 @@
       <c r="J163" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K163" t="str">
+        <v/>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
@@ -5690,6 +6134,9 @@
         <v/>
       </c>
       <c r="J164" t="str">
+        <v/>
+      </c>
+      <c r="K164" t="str">
         <v/>
       </c>
     </row>
